--- a/sample_data/synthetic_pool_research.xlsx
+++ b/sample_data/synthetic_pool_research.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investor_balance_vintageOrigin" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Owner_vs_Investor_CPR_30YR" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Multi_unit_balance_vintage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SF_vs_Mutli_CPR_30YR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SF_vs_Multi_CPR_30YR" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Single_family_market_share" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
